--- a/branches/dev/v2027/StructureDefinition-mii-pr-lungenfunktion-provokationstest.xlsx
+++ b/branches/dev/v2027/StructureDefinition-mii-pr-lungenfunktion-provokationstest.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2490" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2490" uniqueCount="437">
   <si>
     <t>Property</t>
   </si>
@@ -1163,6 +1163,10 @@
   </si>
   <si>
     <t>Need to support individual results, or  groups of results, where the result grouping is arbitrary, but meaningful.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">profile:$this.resolve().code}
+</t>
   </si>
   <si>
     <t>OBXs</t>
@@ -1755,7 +1759,7 @@
     <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="83.859375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="23.03515625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
@@ -6882,7 +6886,7 @@
         <v>79</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>306</v>
+        <v>360</v>
       </c>
       <c r="AC46" s="2"/>
       <c r="AD46" t="s" s="2">
@@ -6910,7 +6914,7 @@
         <v>79</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>79</v>
@@ -6918,13 +6922,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>352</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>353</v>
@@ -6946,7 +6950,7 @@
         <v>79</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L47" t="s" s="2">
         <v>356</v>
@@ -7025,7 +7029,7 @@
         <v>79</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>79</v>
@@ -7033,13 +7037,13 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>352</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>353</v>
@@ -7061,7 +7065,7 @@
         <v>79</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L48" t="s" s="2">
         <v>356</v>
@@ -7140,7 +7144,7 @@
         <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>79</v>
@@ -7148,13 +7152,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>352</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>353</v>
@@ -7176,7 +7180,7 @@
         <v>79</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L49" t="s" s="2">
         <v>356</v>
@@ -7255,7 +7259,7 @@
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>79</v>
@@ -7263,13 +7267,13 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>352</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D50" t="s" s="2">
         <v>353</v>
@@ -7291,7 +7295,7 @@
         <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L50" t="s" s="2">
         <v>356</v>
@@ -7370,7 +7374,7 @@
         <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>79</v>
@@ -7378,13 +7382,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>352</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>353</v>
@@ -7406,7 +7410,7 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L51" t="s" s="2">
         <v>356</v>
@@ -7485,7 +7489,7 @@
         <v>79</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>79</v>
@@ -7493,13 +7497,13 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>352</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D52" t="s" s="2">
         <v>353</v>
@@ -7521,7 +7525,7 @@
         <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L52" t="s" s="2">
         <v>356</v>
@@ -7600,7 +7604,7 @@
         <v>79</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>79</v>
@@ -7608,13 +7612,13 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>352</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D53" t="s" s="2">
         <v>353</v>
@@ -7636,7 +7640,7 @@
         <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L53" t="s" s="2">
         <v>356</v>
@@ -7715,7 +7719,7 @@
         <v>79</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>79</v>
@@ -7723,10 +7727,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7749,16 +7753,16 @@
         <v>79</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7808,7 +7812,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -7834,14 +7838,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -7860,17 +7864,17 @@
         <v>89</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>79</v>
@@ -7919,7 +7923,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -7937,7 +7941,7 @@
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>79</v>
@@ -7945,10 +7949,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8054,10 +8058,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8165,14 +8169,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8194,10 +8198,10 @@
         <v>108</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>111</v>
@@ -8252,7 +8256,7 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -8278,10 +8282,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8307,16 +8311,16 @@
         <v>102</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>79</v>
@@ -8365,7 +8369,7 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
@@ -8391,10 +8395,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8417,13 +8421,13 @@
         <v>89</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8474,7 +8478,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>88</v>
@@ -8500,14 +8504,14 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -8529,14 +8533,14 @@
         <v>102</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>79</v>
@@ -8585,7 +8589,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
@@ -8603,7 +8607,7 @@
         <v>79</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>79</v>
@@ -8611,10 +8615,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8640,10 +8644,10 @@
         <v>223</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8673,10 +8677,10 @@
         <v>153</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>79</v>
@@ -8694,7 +8698,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>77</v>
@@ -8712,7 +8716,7 @@
         <v>79</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>79</v>
@@ -8720,10 +8724,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8829,10 +8833,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8940,10 +8944,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9051,13 +9055,13 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="B66" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="B66" t="s" s="2">
-        <v>422</v>
-      </c>
       <c r="C66" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D66" t="s" s="2">
         <v>79</v>
@@ -9101,7 +9105,7 @@
         <v>79</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="T66" t="s" s="2">
         <v>79</v>
@@ -9166,10 +9170,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C67" t="s" s="2">
         <v>250</v>
@@ -9216,7 +9220,7 @@
         <v>79</v>
       </c>
       <c r="S67" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="T67" t="s" s="2">
         <v>79</v>
@@ -9235,7 +9239,7 @@
       </c>
       <c r="Y67" s="2"/>
       <c r="Z67" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>79</v>
@@ -9279,10 +9283,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9392,10 +9396,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9418,19 +9422,19 @@
         <v>79</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>79</v>
@@ -9479,7 +9483,7 @@
         <v>79</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>77</v>
@@ -9497,7 +9501,7 @@
         <v>79</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>79</v>

--- a/branches/dev/v2027/StructureDefinition-mii-pr-lungenfunktion-provokationstest.xlsx
+++ b/branches/dev/v2027/StructureDefinition-mii-pr-lungenfunktion-provokationstest.xlsx
@@ -1386,7 +1386,7 @@
   </si>
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
-  &lt;system value="http://snomed.info/sct|http://snomed.info/sct/900000000000207008/version/20260701"/&gt;
+  &lt;system value="http://snomed.info/sct"/&gt;
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
